--- a/stufe-5/med/extract-amts-from-ig-ptdata-1884/StructureDefinition-ISiKKontaktGesundheitseinrichtung.xlsx
+++ b/stufe-5/med/extract-amts-from-ig-ptdata-1884/StructureDefinition-ISiKKontaktGesundheitseinrichtung.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.1</t>
+    <t>6.0.0-rc</t>
   </si>
   <si>
     <t>Name</t>
